--- a/StructureDefinition-Revisionshistorik.xlsx
+++ b/StructureDefinition-Revisionshistorik.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Revisionshistorik.xlsx
+++ b/StructureDefinition-Revisionshistorik.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="101">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -254,46 +254,72 @@
     <t>Source attribute: Version 4.0 RC2; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Ny version 4.0 av laboratoriesvarskontrakt som stödjer mikrobiologiska svar. Förarbete av Fredrik Ström och Helena Antonsson.</t>
+  </si>
+  <si>
     <t>Revisionshistorik.Version40RC5</t>
   </si>
   <si>
     <t>Source attribute: Version 4.0 RC5; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Fortsatt arbete där koppling till kodverk har förtydligats. Vissa specifika klasser har bytts ut till generiska kombinationer av analys/analysresultat. Begreppsmodellering och terminologi i enlighet med Socialstyrelsens termbank och Nationella Informationsstruktur.</t>
+  </si>
+  <si>
     <t>Revisionshistorik.Version40RC6</t>
   </si>
   <si>
     <t>Source attribute: Version 4.0 RC6; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Utökade attribut för analysutrustning.
+Möjlighet för mottagare att signera enskilda resultat förutom hela svaret
+Ändrad kardinalitet på signatur från ansvarig för svar.</t>
+  </si>
+  <si>
     <t>Revisionshistorik.Version40RC9</t>
   </si>
   <si>
     <t>Source attribute: Version 4.0 RC9; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Lagt till coding strength på CV-datatyp (CNE - Coded with No Exceptions och CWE - Coded With Exceptions)</t>
+  </si>
+  <si>
     <t>Revisionshistorik.Version40</t>
   </si>
   <si>
     <t>Source attribute: Version 4.0; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Ny informationsspecifikation för laboratoriesvar fastställd.</t>
+  </si>
+  <si>
     <t>Revisionshistorik.Version401</t>
   </si>
   <si>
     <t>Source attribute: Version 4.0.1; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Uppdaterat samtliga urval.</t>
+  </si>
+  <si>
     <t>Revisionshistorik.f402</t>
   </si>
   <si>
     <t>Source attribute: 4.0.2; type could not be resolved from source model</t>
   </si>
   <si>
+    <t>Uppdaterade tomma fält i beskrivningen av informationsmodellen.</t>
+  </si>
+  <si>
     <t>Revisionshistorik.Version41</t>
   </si>
   <si>
     <t>Source attribute: Version 4.1; type could not be resolved from source model</t>
+  </si>
+  <si>
+    <t>Uppdaterat beskrivningen för olika typer av signeringar.</t>
   </si>
 </sst>
 </file>
@@ -879,7 +905,7 @@
         <v>78</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -947,10 +973,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -976,10 +1002,10 @@
         <v>77</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1030,7 +1056,7 @@
         <v>19</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>71</v>
@@ -1047,10 +1073,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1076,10 +1102,10 @@
         <v>77</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1130,7 +1156,7 @@
         <v>19</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>71</v>
@@ -1147,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1176,10 +1202,10 @@
         <v>77</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1230,7 +1256,7 @@
         <v>19</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>71</v>
@@ -1247,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1276,10 +1302,10 @@
         <v>77</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1330,7 +1356,7 @@
         <v>19</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>71</v>
@@ -1347,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1376,10 +1402,10 @@
         <v>77</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1430,7 +1456,7 @@
         <v>19</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>71</v>
@@ -1447,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1476,10 +1502,10 @@
         <v>77</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1530,7 +1556,7 @@
         <v>19</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>71</v>
@@ -1547,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1576,10 +1602,10 @@
         <v>77</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1630,7 +1656,7 @@
         <v>19</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>71</v>
